--- a/ig/nr-change-signes-vitaux-display/observations-summary.xlsx
+++ b/ig/nr-change-signes-vitaux-display/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="60">
   <si>
     <t>Profile</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>null#8867-4</t>
+  </si>
+  <si>
+    <t>mesures-fr-observation-oxygen-sat</t>
+  </si>
+  <si>
+    <t>MesFrObservationOxygenSat</t>
+  </si>
+  <si>
+    <t>null#2708-6</t>
   </si>
   <si>
     <t>mesures-observation-glucose</t>
@@ -316,7 +325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -683,16 +692,16 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>19</v>
@@ -706,25 +715,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F12" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="C12" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s" s="2">
+      <c r="G12" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="F12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>23</v>
@@ -759,7 +768,7 @@
         <v>14</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>23</v>
@@ -791,10 +800,10 @@
         <v>53</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>23</v>
@@ -826,7 +835,7 @@
         <v>56</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>17</v>
@@ -841,6 +850,41 @@
         <v>14</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K16" t="s" s="2">
         <v>14</v>
       </c>
     </row>
